--- a/Vier wöchige YLA/Unterrichtsplan_mit_Personenzuteilungen_Woche3.xlsx
+++ b/Vier wöchige YLA/Unterrichtsplan_mit_Personenzuteilungen_Woche3.xlsx
@@ -586,7 +586,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>[Karuna] Praxis: Intensives Pranayama, Mudras.. Bandhas: Die höheren Stufen des Hatha Yoga (bis 9.00 Uhr) (Notiz: Satsang Tripura)</t>
+          <t>[Karuna] Praxis: Intensives Pranayama, Mudras.. Bandhas: Die höheren Stufen des Hatha Yoga (Notiz: Satsang Tripura)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>6:00–9:00</t>
+          <t>6:00–8:35</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>6:00–8:35</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>6:00–9:00</t>
+          <t>6:00–8:35</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>6:00–8:35</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -3588,7 +3588,7 @@
 12.09.2026 20:00 – Energiemeditation / langer Satsang
 13.09.2026 6:00–8:35 – 7 Bhumikas, Teil 2
 13.09.2026 14:35 – Bhakti Yoga: 5 Bhavas und 9 Formen von Bhakti
-15.09.2026 6:00–9:00 – Praxis: Intensives Pranayama, Mudras.. Bandhas (bis 9:00)
+15.09.2026 6:00–8:35 – Praxis: Intensives Pranayama, Mudras.. Bandhas (bis 9:00)
 15.09.2026 19:00 – Info Mantra-Einweihung
 16.09.2026 14:35 – Yoga und Streß-Management, Teil 1
 16.09.2026 19:00 – Die 8 Maha-Kumbhakas; Die 5 Pranas und ihre Sublimierung; Ojas
